--- a/assets/docs/lop3/Dao duc - Lop 3.xlsx
+++ b/assets/docs/lop3/Dao duc - Lop 3.xlsx
@@ -718,7 +718,8 @@
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Quan tâm hàng xóm láng giềng”, GV chiếu bộ ảnh việc làm quen thuộc trong xóm như trông giúp nhà bên, đưa cụ già qua đường, cùng dọn ngõ sau mưa
-Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các tình huống trên màn hình và cho HS chọn cách ứng xử phù hợp khi nhà hàng xóm có việc, khi em ở nhà một mình mà người lạ gọi cửa</t>
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các tình huống trên màn hình và cho HS chọn cách ứng xử phù hợp khi nhà hàng xóm có việc, khi em ở nhà một mình mà người lạ gọi cửa
+Học tập và làm theo Bác: Điều 1 “Yêu Tổ quốc, yêu đồng bào” (mạch 1): HS hiểu yêu đồng bào bắt đầu từ quan tâm người ở gần mình; nêu một việc vừa sức sẽ làm cho hàng xóm trong tuần (hỏi thăm, giữ yên lặng khi bác ốm, trông em giúp).</t>
         </is>
       </c>
     </row>
